--- a/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CDCF782-E99D-49FD-9116-9C27655C239E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8ABAD24-CB7A-4FC0-9377-90DECAE33404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B3796BE6-8BB6-4C2B-B54A-908428D33DBE}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{260241A9-41CF-4B63-917F-82E8949BC486}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1585,7 +1585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53404311-7060-4D42-B8CA-D9CEE0179566}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93A1FA7B-654D-47A9-87AE-73423C32CF9D}">
   <dimension ref="B3:L160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8ABAD24-CB7A-4FC0-9377-90DECAE33404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE8A9708-47DF-4666-8038-31342C7B4F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{260241A9-41CF-4B63-917F-82E8949BC486}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{502DB2B8-C268-43D7-B4AF-2862AB34C65F}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1585,7 +1585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93A1FA7B-654D-47A9-87AE-73423C32CF9D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F9B4E09-822E-4A3A-9F1E-70BD36CC3E54}">
   <dimension ref="B3:L160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE8A9708-47DF-4666-8038-31342C7B4F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DCE0CBC-B940-487F-9B27-4C7BF43F0B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{502DB2B8-C268-43D7-B4AF-2862AB34C65F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D6CF1C23-16C5-4DA3-B7A9-2B626FCA33FB}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1585,7 +1585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F9B4E09-822E-4A3A-9F1E-70BD36CC3E54}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F87007B-D990-4CE8-B9EA-E31E02E5B237}">
   <dimension ref="B3:L160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DCE0CBC-B940-487F-9B27-4C7BF43F0B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7C5E000-D41E-41AB-A912-A26612BFFDBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D6CF1C23-16C5-4DA3-B7A9-2B626FCA33FB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{40085C05-F8FC-499C-8155-EE333829D6C5}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1585,7 +1585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F87007B-D990-4CE8-B9EA-E31E02E5B237}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60581EF-AE52-4F42-B555-906CC1FC09FB}">
   <dimension ref="B3:L160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7C5E000-D41E-41AB-A912-A26612BFFDBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BBE090D-6FA8-405C-8114-C941D4E21353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{40085C05-F8FC-499C-8155-EE333829D6C5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{85883F77-9312-4554-9FDE-E47E0BE8588C}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1585,7 +1585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60581EF-AE52-4F42-B555-906CC1FC09FB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8578E63-C1F7-4EC0-A3EB-0300DCF44DD4}">
   <dimension ref="B3:L160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BBE090D-6FA8-405C-8114-C941D4E21353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3AC4ACF-BD68-4F55-983F-DF801BD079D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{85883F77-9312-4554-9FDE-E47E0BE8588C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{383A980C-D353-44DF-B60D-DF7B92B2D6A0}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1585,7 +1585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8578E63-C1F7-4EC0-A3EB-0300DCF44DD4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5DB074F-2085-4C2E-9181-0E0AB6CA3C7A}">
   <dimension ref="B3:L160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3AC4ACF-BD68-4F55-983F-DF801BD079D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{32B759D0-F7A3-408D-849F-88411B40DE8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{383A980C-D353-44DF-B60D-DF7B92B2D6A0}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B83D90E6-EA41-410D-A6E9-D6581EA2424C}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1585,7 +1585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5DB074F-2085-4C2E-9181-0E0AB6CA3C7A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E2A18FE-07EF-42FF-912F-138FDFB83CF2}">
   <dimension ref="B3:L160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{32B759D0-F7A3-408D-849F-88411B40DE8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A37C810-BB80-407B-8EBA-9E30E115CA75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B83D90E6-EA41-410D-A6E9-D6581EA2424C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{BDEA23BA-B67F-478C-B7A2-E42D23C87F9F}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1585,7 +1585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E2A18FE-07EF-42FF-912F-138FDFB83CF2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{583D2BDA-B41B-4D52-BE2E-1F4CCF93809F}">
   <dimension ref="B3:L160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A37C810-BB80-407B-8EBA-9E30E115CA75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8904F4B5-828A-4D7E-BABD-3943CA52E580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{BDEA23BA-B67F-478C-B7A2-E42D23C87F9F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1D12AEBD-C5E1-441E-B8AD-CB57D7273EAC}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1585,7 +1585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{583D2BDA-B41B-4D52-BE2E-1F4CCF93809F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12B6A416-B256-4953-883E-65A96A5E5AA5}">
   <dimension ref="B3:L160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8904F4B5-828A-4D7E-BABD-3943CA52E580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DE1D8E9-AF61-4534-A14F-4D712BB772D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1D12AEBD-C5E1-441E-B8AD-CB57D7273EAC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{312D416B-520A-44EF-AA45-5A6F2CD9B454}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1585,7 +1585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12B6A416-B256-4953-883E-65A96A5E5AA5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BEC92A6-22E9-4E05-A126-47E2A817F46D}">
   <dimension ref="B3:L160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DE1D8E9-AF61-4534-A14F-4D712BB772D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E704505-6094-42BC-9A07-A12B172B17BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{312D416B-520A-44EF-AA45-5A6F2CD9B454}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0297E894-89F5-4E8B-9B36-7C2B272282A5}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1585,7 +1585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BEC92A6-22E9-4E05-A126-47E2A817F46D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{888A7EB4-9F35-4656-9FC0-8403C5D17FD6}">
   <dimension ref="B3:L160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E704505-6094-42BC-9A07-A12B172B17BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED16C06C-108E-4185-A023-C2024566544C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0297E894-89F5-4E8B-9B36-7C2B272282A5}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="12682" xr2:uid="{6DB60477-92A6-478E-AFF3-C5DB319EA2A9}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1585,7 +1585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{888A7EB4-9F35-4656-9FC0-8403C5D17FD6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A422A1C-8BFF-47A4-9B96-FCCEF75E35D1}">
   <dimension ref="B3:L160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED16C06C-108E-4185-A023-C2024566544C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B7B1FBF-4411-4B97-8C50-8430FA5193C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="12682" xr2:uid="{6DB60477-92A6-478E-AFF3-C5DB319EA2A9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6644C121-414F-42C7-B56A-2E3B1FB56FE1}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1585,7 +1585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A422A1C-8BFF-47A4-9B96-FCCEF75E35D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C47524D1-28E1-4AE3-9543-B8A53AE8CC5C}">
   <dimension ref="B3:L160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B7B1FBF-4411-4B97-8C50-8430FA5193C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{68D25B4B-FDE3-4E73-AB7F-A7BE8C70CBC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6644C121-414F-42C7-B56A-2E3B1FB56FE1}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D8CD205E-BE59-4D7C-8B80-5277C3CA2942}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1585,7 +1585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C47524D1-28E1-4AE3-9543-B8A53AE8CC5C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3963575-471A-4635-B9DA-9C01679BCF83}">
   <dimension ref="B3:L160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68D25B4B-FDE3-4E73-AB7F-A7BE8C70CBC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF60C2CE-5091-45ED-B794-FF356C470BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D8CD205E-BE59-4D7C-8B80-5277C3CA2942}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A67CF6AE-372F-451A-8B84-F1C6F3CBBDC9}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1585,7 +1585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3963575-471A-4635-B9DA-9C01679BCF83}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D74FBCB-B0DA-49AD-B35D-A685BCD67D27}">
   <dimension ref="B3:L160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF60C2CE-5091-45ED-B794-FF356C470BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4820E15-5F07-409C-A762-6538E6150C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A67CF6AE-372F-451A-8B84-F1C6F3CBBDC9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EA63F65C-5A3D-417C-8323-0FC05D450A30}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1585,7 +1585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D74FBCB-B0DA-49AD-B35D-A685BCD67D27}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7AD9006-1C2C-46F0-B0FB-BDF459C7A9A0}">
   <dimension ref="B3:L160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
